--- a/data/trans_bre/IQ2605_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,94%</t>
+          <t>-2,35%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 13,67</t>
+          <t>-8,81; 13,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 6,88</t>
+          <t>-16,24; 6,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 5,05</t>
+          <t>-13,91; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 17,56</t>
+          <t>-20,94; 17,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 30,12</t>
+          <t>-15,62; 28,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 10,15</t>
+          <t>-21,26; 9,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 6,16</t>
+          <t>-16,02; 6,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 28,15</t>
+          <t>-25,09; 26,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,03%</t>
+          <t>-0,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 12,36</t>
+          <t>-10,23; 13,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 21,78</t>
+          <t>0,01; 22,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 0,51</t>
+          <t>-15,91; 0,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 21,1</t>
+          <t>-21,28; 22,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 23,94</t>
+          <t>-15,83; 24,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 36,77</t>
+          <t>0,1; 37,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 0,59</t>
+          <t>-17,89; 0,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 35,02</t>
+          <t>-25,5; 38,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,18</t>
+          <t>-10,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,32%</t>
+          <t>-16,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 11,61</t>
+          <t>-15,75; 10,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 13,13</t>
+          <t>-10,9; 11,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 4,0</t>
+          <t>-20,37; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 20,06</t>
+          <t>-43,47; 19,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 23,08</t>
+          <t>-26,07; 19,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 19,56</t>
+          <t>-13,99; 16,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 5,55</t>
+          <t>-24,91; 4,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 41,65</t>
+          <t>-59,44; 38,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-14,75</t>
+          <t>-15,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,5%</t>
+          <t>-18,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 14,6</t>
+          <t>-0,9; 15,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 1,82</t>
+          <t>-12,31; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 3,66</t>
+          <t>-9,06; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 2,14</t>
+          <t>-31,58; 0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 30,72</t>
+          <t>-1,82; 31,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 2,38</t>
+          <t>-14,72; 2,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 4,9</t>
+          <t>-11,09; 5,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 2,8</t>
+          <t>-35,05; 0,13</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,1%</t>
+          <t>-1,33%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 10,81</t>
+          <t>-10,67; 10,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 12,17</t>
+          <t>-5,85; 12,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 4,83</t>
+          <t>-11,31; 5,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 14,8</t>
+          <t>-20,52; 15,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 23,98</t>
+          <t>-20,12; 22,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 19,66</t>
+          <t>-8,06; 20,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 6,04</t>
+          <t>-13,51; 6,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 19,21</t>
+          <t>-24,24; 19,97</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-1,13%</t>
+          <t>-0,03%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 8,67</t>
+          <t>-19,9; 8,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 12,54</t>
+          <t>-13,4; 12,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 20,26</t>
+          <t>-5,89; 21,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 21,92</t>
+          <t>-34,99; 25,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 22,86</t>
+          <t>-37,63; 20,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 17,48</t>
+          <t>-16,59; 17,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 35,69</t>
+          <t>-7,98; 39,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 33,98</t>
+          <t>-44,4; 41,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,27</t>
+          <t>-5,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,83%</t>
+          <t>-7,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 6,34</t>
+          <t>-2,44; 6,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,67</t>
+          <t>-4,15; 3,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 0,63</t>
+          <t>-6,98; 0,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 3,17</t>
+          <t>-14,19; 2,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 12,68</t>
+          <t>-4,5; 12,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,1</t>
+          <t>-5,48; 5,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 0,75</t>
+          <t>-8,67; 0,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 4,56</t>
+          <t>-17,64; 3,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2605_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-6,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-4,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-2,35%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.355903058525788</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.512776197668855</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.697931322864023</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.774312946300316</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.04394844969462669</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.06254458736971777</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.04378754178502692</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.02350694451726998</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,81; 13,64</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,24; 6,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,91; 5,37</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-20,94; 17,03</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-15,62; 28,21</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-21,26; 9,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,02; 6,83</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-25,09; 26,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.810653064725773</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.24292570922301</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.91448894938275</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-20.94466845032197</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1562249803711897</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2126237297138687</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1602182572055419</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2509461974280616</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.63942642922445</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.599927506307026</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.371901564709171</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.03444176218651</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2820929329332862</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.09584574824904514</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.0683110821020652</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2623809421280837</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,57</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-7,47</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-8,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-0,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-10,23; 13,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 22,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-15,91; 0,76</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-21,28; 22,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-15,83; 24,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 37,65</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-17,89; 0,95</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-25,5; 38,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.9568048250713002</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>11.57149839925852</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-7.467117864713291</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4271816268946793</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01591909214617535</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1756224808588985</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.08677014055289739</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.005864160663369651</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,07</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-8,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-10,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-16,39%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-10.22929791593514</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01453746576210243</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-15.90938150465618</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-21.27856368135291</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1582706880622548</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.00101208524515747</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1789113451604139</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2550469729333307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,75; 10,29</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,9; 11,11</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,37; 3,2</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-43,47; 19,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-26,07; 19,88</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-13,99; 16,37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-24,91; 4,46</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-59,44; 38,63</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.80926132550461</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.14716703912709</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7570112070179287</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>22.25106221020264</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2453962393138901</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3765410266363713</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.009452872158605704</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3817986564541459</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,84</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,82</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-18,47%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.067172622062186</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.465838706892896</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-8.176686706362391</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-10.51656509155784</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.03748084689926021</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.006344997737701413</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.104766562481299</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1639270177923557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 15,04</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,31; 1,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,06; 4,23</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-31,58; 0,2</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 31,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-14,72; 2,06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-11,09; 5,64</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-35,05; 0,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.74545079941641</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.90449781239325</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-20.36877835600249</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-43.46748879414955</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2606533556822649</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1398581994306756</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2491201335810182</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5943787172034131</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.28548217348935</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.11113923751631</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.200812400388246</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.78995123090822</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1988483682179147</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1637494308008464</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.04462983609586237</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3863212937408476</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-4,53%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-1,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,67; 10,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 12,83</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-11,31; 5,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-20,52; 15,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-20,12; 22,24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-8,06; 20,16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 6,37</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-24,24; 19,97</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>6.839347588589395</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-5.164894268249032</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.82347856685734</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-15.54529411170974</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1315113411280551</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06512254143907927</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03613456541802278</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1846604598034295</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-5,41</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7,8</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-11,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-0,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-0,03%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.9036814209334091</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-12.30763457887768</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.055945416849315</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-31.57733027373681</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.01818005096803439</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1472026379012396</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1109133421046463</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3505206330877442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-19,9; 8,04</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-13,4; 12,29</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-5,89; 21,89</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-34,99; 25,25</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-37,63; 20,17</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-16,59; 17,24</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,98; 39,4</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-44,4; 41,48</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.04372994864123</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.545613967758638</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.226413448167993</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.1957183975023674</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3160101008936299</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0205608689716691</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.05639574585424838</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.001332002942783128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,96</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-4,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-7,73%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.1498441783293947</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.836375565317473</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.622916856841063</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.086481731951605</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.00297484809255901</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.04109660174765335</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.04534484950804561</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.01334390107683183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,44; 6,4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 3,64</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-6,98; 0,37</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-14,19; 2,59</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-4,5; 12,62</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-5,48; 5,15</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-8,67; 0,46</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-17,64; 3,46</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.67468615385245</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.847629699112256</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-11.30520728570694</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-20.52102017603348</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2012218047943087</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.08063332090676535</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1350776542868679</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2423547330550381</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>10.28940384945284</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.83283604548023</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.003004350006155</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15.06068954805678</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2224130888240463</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2015788739462199</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.06366832076630041</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1996669050856404</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-5.41282940440479</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.4061383322953027</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>7.804525224390413</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.02174643478205507</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1188640025645267</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.005306413785180785</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.1216010978390989</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.0003061442845661549</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-19.89868212453868</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-13.40343304619008</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-5.888956134641485</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-34.98621136679026</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3762537550017861</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1658788158008032</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.07979722860050346</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.4439675503585983</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>8.042419967615661</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>12.28555527112918</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>21.89167400561731</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>25.25210174103765</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2017045742884342</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1723582104527622</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.3939532031792882</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.4147978062986565</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.72779495108516</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1783701329761134</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-3.404016125751341</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-5.957656937457589</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.03274988391627329</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.002425364507410927</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.04294416758730596</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.07732856473501629</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.44053604866357</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.150284587820425</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-6.979835042253407</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-14.18975733249052</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.04502711409434679</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.05476533896079212</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.08669963708104618</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1763935903715429</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.398546181391815</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.63691416652638</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3671858911298318</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.589141529203445</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.1261705553585752</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.05146458392376213</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.004600361253211367</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.03461227335774587</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
